--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18067,6 +18067,717 @@
       </c>
       <c r="AA157" s="4" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>The Green Hatch Oü</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>The Green Hatch Oü</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>22354</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>94 Peterburi tee</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>11415</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://thegreenhatch.com</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>info@thegreenhatch.com</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>12119491</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr"/>
+      <c r="S158" s="2" t="inlineStr"/>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>Anna Koponen</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anna-koponen-3a848791/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>The Green Hatch Oü</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>The Green Hatch Oü</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>22354</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>94 Peterburi tee</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>11415</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://thegreenhatch.com</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>info@thegreenhatch.com</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr"/>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>12119491</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr"/>
+      <c r="S159" s="2" t="inlineStr"/>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>Mikael Harthin</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Sanitex Oü</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Sanitex Oü</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>54056</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Rae</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>1 Graniidi tee</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>75310</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://sanitex.ee</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>sanitex.estonia@sanitex.eu</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+372 622 6399</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>11931003</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sanitex-eesti/</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr"/>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>Viktor Naumov</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>Head of the Commercial Department</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/viktor-naumov/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Sanitex Oü</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Sanitex Oü</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>54056</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Rae</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>1 Graniidi tee</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>75310</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://sanitex.ee</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>sanitex.estonia@sanitex.eu</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>+372 622 6399</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>11931003</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sanitex-eesti/</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr"/>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>Elli Sepp</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elli-sepp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Sanitex Oü</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Sanitex Oü</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>54056</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Rae</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>1 Graniidi tee</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>75310</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://sanitex.ee</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>sanitex.estonia@sanitex.eu</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>+372 622 6399</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>11931003</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sanitex-eesti/</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr"/>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandra Obraztsova</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aleksandra-obraztsova-3583592b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Oro Trade Oü</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Oro Trade Oü</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>54079</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>4/6 Padriku tee</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>11912</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://oro.ee</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>info@oro.ee</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr"/>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>12124925</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr"/>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/OroTrade/</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr"/>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>Lauri Mõtsnik</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lauri-m%C3%B5tsnik-57820927/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Worldwide Export-import Oü</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Wines of Portugal </t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>51474</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>16 Kõivu tee</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>12113</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://portugal-wines.com</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>info@portugal-wines.com</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr"/>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>11095498</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr"/>
+      <c r="S164" s="2" t="inlineStr"/>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>Kristiina De</t>
+        </is>
+      </c>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristiina-de-castro-ribeiro/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA164"/>
+  <dimension ref="A1:AA168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18778,6 +18778,378 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Momentin Eesti Oü</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Momentin Eesti Oü</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>51787</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>3 Siduri</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://momentinbaltics.com</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>momentineesti@momentingroup.com</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>+372 646 4565</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>301432553</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr"/>
+      <c r="S165" s="2" t="inlineStr"/>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/momentineesti/</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr"/>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Vino Nobile Pood Oü</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Vino Nobile Pood Oü</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>42120</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>5 Herne</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinonobile.ee</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>pood@vinonobile.ee</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>16366217</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinoNobileVeinipood/?rc=p</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinonobile_veinipood/</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>Tiina Sarapuu</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Vino Nobile Pood Oü</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Vino Nobile Pood Oü</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>42120</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>5 Herne</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinonobile.ee</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>pood@vinonobile.ee</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr"/>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>16366217</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr"/>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinoNobileVeinipood/?rc=p</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinonobile_veinipood/</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>Triin Kruus</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Pbi Wines Oü</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Pbi Wines Oü</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>54149</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Tartu</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Tartu maakond</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>45 Vanemuise</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>51003</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://winepassion.ee</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>info@winepassion.ee</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr"/>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>12751645</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr"/>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WinePassionVeinipood</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winepassion_veinipood/</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr"/>
+      <c r="X168" s="2" t="inlineStr"/>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA168"/>
+  <dimension ref="A1:AA176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19150,6 +19150,774 @@
       <c r="Z168" s="2" t="inlineStr"/>
       <c r="AA168" s="2" t="inlineStr"/>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>WINE CRAFT Osauhing</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr"/>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>167812</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Narva</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>A. Puskini tn 9-17</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>20309</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://winecraft.ee</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>748681</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>order@winecraft.ee</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr"/>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>14160026</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-craft-ou/</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61567163773632</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecraft_est/</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>Igor Korban</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igorkorban/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>WINE CRAFT Osauhing</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>167812</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Narva</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>A. Puskini tn 9-17</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>20309</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://winecraft.ee</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>748681</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>order@winecraft.ee</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr"/>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>14160026</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-craft-ou/</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61567163773632</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecraft_est/</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandr Tedeev</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aleksandr-tedeev-09a1473b9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>OU Burrata</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr"/>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>167809</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Miiduranna kula</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Tuulekivi tee 7</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>74015</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.burrata.ee</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>34621</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>info@burrata.ee</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr"/>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>16538138</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr"/>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61573123769857</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/burrata.ee/</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>Kaspar Koitla</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kaspar-koitla-652056212/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Mulligalerii Mtü</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Mulligalerii Mtü</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>54061</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>25 Tatari</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>10116</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://mulligalerii.ee</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>info@mulligalerii.ee</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr"/>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>80421307</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Mulligalerii/</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>Kristel Voltenberg</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kristel-voltenberg-64a51028</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Momentin Eesti Oü</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Momentin Eesti Oü</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>51787</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>3 Siduri</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://momentinbaltics.com</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>momentineesti@momentingroup.com</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>+372 646 4565</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>301432553</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/momentineesti/</t>
+        </is>
+      </c>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr"/>
+      <c r="W173" s="2" t="inlineStr"/>
+      <c r="X173" s="2" t="inlineStr"/>
+      <c r="Y173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Vino Nobile Pood Oü</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Vino Nobile Pood Oü</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>42120</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>5 Herne</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinonobile.ee</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>pood@vinonobile.ee</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr"/>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>16366217</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr"/>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinoNobileVeinipood/?rc=p</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinonobile_veinipood/</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr"/>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>Tiina Sarapuu</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr"/>
+      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Vino Nobile Pood Oü</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Vino Nobile Pood Oü</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>42120</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>5 Herne</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinonobile.ee</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>pood@vinonobile.ee</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr"/>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>16366217</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr"/>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinoNobileVeinipood/?rc=p</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinonobile_veinipood/</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr"/>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>Triin Kruus</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Pbi Wines Oü</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Pbi Wines Oü</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>54149</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Tartu</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Tartu maakond</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>45 Vanemuise</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>51003</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://winepassion.ee</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>info@winepassion.ee</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr"/>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>12751645</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WinePassionVeinipood</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winepassion_veinipood/</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr"/>
+      <c r="W176" s="2" t="inlineStr"/>
+      <c r="X176" s="2" t="inlineStr"/>
+      <c r="Y176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA176"/>
+  <dimension ref="A1:AA191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19918,6 +19918,1429 @@
       <c r="Z176" s="2" t="inlineStr"/>
       <c r="AA176" s="2" t="inlineStr"/>
     </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>ACE OF WINE OU</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr"/>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>167879</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Mustamae tee 6b</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>10616</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>https://aceofwine.ee</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>1985010</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>info@aceofwine.ee</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr"/>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>17151803</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr"/>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100094455064539</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aceofwine/</t>
+        </is>
+      </c>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr"/>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>Irene Tooma</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>Board Member</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Momentin Estonia OÜ</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Momentin Estonia OÜ</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>167863</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>3 Siduri</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.momentin.ee</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>epood@momentin.ee</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>+372 600 8026</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>31355605</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/momentin-eesti/</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/momentineesti</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/momentineesti/</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr"/>
+      <c r="X178" s="2" t="inlineStr"/>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Rasa Trading Company As</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Rasa Trading Company As</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>3959</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>4 Kollane</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>10147</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>https://rasatrading.ee</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>sales@rasatrading.ee</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>+372 601 4650</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>10588230</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr"/>
+      <c r="S179" s="2" t="inlineStr"/>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr">
+        <is>
+          <t>Mahesh Ramnani</t>
+        </is>
+      </c>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mahesh-ramnani-9b7643135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Rasa Trading Company As</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Rasa Trading Company As</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>3959</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>4 Kollane</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>10147</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://rasatrading.ee</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>sales@rasatrading.ee</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>+372 601 4650</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>10588230</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr"/>
+      <c r="S180" s="2" t="inlineStr"/>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr">
+        <is>
+          <t>Piret Poldsaar</t>
+        </is>
+      </c>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piret-poldsaar-5261b624/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Jussi Joogid Oü</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Jussi Joogid Oü</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>44221</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Pärnu</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Pärnu maakond</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>24 Nikolai</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>80014</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>https://jussinviinakauppa.ee</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>jussin.viinakauppa@gmail.com</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>+372 442 0310</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr"/>
+      <c r="Q181" s="2" t="inlineStr"/>
+      <c r="R181" s="2" t="inlineStr"/>
+      <c r="S181" s="2" t="inlineStr"/>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr">
+        <is>
+          <t>Jouni Juhani</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>As Monotal</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>As Monotal</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>3956</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>22 Plasti</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>13619</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>https://winelist.ee</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>pood@winelist.ee</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>+372 635 0133</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>10047712</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr"/>
+      <c r="S182" s="2" t="inlineStr"/>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr"/>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Da Vinci Food Oü</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Da Vinci Food Oü</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>3942</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>4 Mõisa</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>13522</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://davincifood.ee</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>sales@davincifood.ee</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>+372 681 0000</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>11384908</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/davincifood</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/davincifood.ee/</t>
+        </is>
+      </c>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>Aleksander Ugur</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aleksander-ugur-656156204/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Da Vinci Food Oü</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Da Vinci Food Oü</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>3942</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>4 Mõisa</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>13522</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://davincifood.ee</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>sales@davincifood.ee</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>+372 681 0000</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>11384908</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr"/>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/davincifood</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/davincifood.ee/</t>
+        </is>
+      </c>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>Janek Neltsas</t>
+        </is>
+      </c>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>Food &amp; Beverages Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/janek-neltsas-8994309b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Balen Oü</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Balen Oü</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>3936</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Peetri</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>1 Läike tee põik</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>75312</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://balen.ee</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>balen@balen.ee</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>+372 600 0950</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>10448552</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr"/>
+      <c r="S185" s="2" t="inlineStr"/>
+      <c r="T185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr">
+        <is>
+          <t>Robert Vahur</t>
+        </is>
+      </c>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-vahur-3a81772/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Balen Oü</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Balen Oü</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>3936</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Peetri</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>1 Läike tee põik</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>75312</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://balen.ee</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>balen@balen.ee</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>+372 600 0950</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>10448552</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr"/>
+      <c r="S186" s="2" t="inlineStr"/>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr">
+        <is>
+          <t>Tarmo Smalko</t>
+        </is>
+      </c>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tarmo-smalko-95735165/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Bollicine Oü</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Bollicine Oü</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>41040</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>6 Fr. R. Faehlmanni</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>10125</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://tellivein.com</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>bollicineoy@hotmail.com</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr"/>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>11440328</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr"/>
+      <c r="S187" s="2" t="inlineStr"/>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr"/>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Vabrik Vinoteek</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Vabrik Vinoteek</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>6 Vabriku tänav</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>10414</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>http://www.vabrik.eu</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>vabrik@vabrik.eu</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr"/>
+      <c r="P188" s="2" t="inlineStr"/>
+      <c r="Q188" s="2" t="inlineStr"/>
+      <c r="R188" s="2" t="inlineStr"/>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vabrikvinoteek</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vabrik.vinoteek</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr">
+        <is>
+          <t>Peremees André</t>
+        </is>
+      </c>
+      <c r="X188" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peremees-andr%C3%A9-030b9b15/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Hansson Holding Oü</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Hansson Holding Oü</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>54224</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Viimsi</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>14 Nelgi põik</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>74001</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>https://hanssonholding.com</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr"/>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>info@hanssonholding.com</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr"/>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>14868713</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hansson-holding-o%C3%BC/</t>
+        </is>
+      </c>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gourmetandwinediscovery/</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hansson_holding/</t>
+        </is>
+      </c>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr">
+        <is>
+          <t>Evelin Hansson</t>
+        </is>
+      </c>
+      <c r="X189" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/evelin-hansson-hansson-holding/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Araxes Oü</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Araxes Oü</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>34088</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Harju</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Tartu Mnt 84a – 201</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>10112</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://araxes.ee</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>info@araxes.ee</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>+372 662 3648</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>14694153</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="inlineStr"/>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/araxeseesti/</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/araxes.ee/</t>
+        </is>
+      </c>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr"/>
+      <c r="W190" s="2" t="inlineStr"/>
+      <c r="X190" s="2" t="inlineStr"/>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Bottlescouts Oü</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Bottlescouts Oü</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>52158</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>8 Mere puiestee</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>10111</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://bottlescouts.com</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>info@bottlescouts.com</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr"/>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>11733036</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr"/>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Bottlescouts/</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bottlescouts/</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr">
+        <is>
+          <t>Katrin Oja</t>
+        </is>
+      </c>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>Country and Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katrin-oja-6b68629b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA191"/>
+  <dimension ref="A1:AA195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21341,6 +21341,430 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Estonia Oü</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Estonia Oü</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>29354</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>46-519 Peterburi tee</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>11415</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://amberdistribution.ee</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>info@amberdistribution.ee</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>+372 613 9799</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>10641409</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr"/>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Amber-Distribution-Estonia-616752232134626/</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amberdistributionestonia</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr"/>
+      <c r="W192" s="2" t="inlineStr">
+        <is>
+          <t>Kärolin Raudsepp</t>
+        </is>
+      </c>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>Spirits Category Manager</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/k%C3%A4rolin-raudsepp-5b1812162/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Estonia Oü</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Amber Distribution Estonia Oü</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>29354</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>46-519 Peterburi tee</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>11415</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://amberdistribution.ee</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>info@amberdistribution.ee</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>+372 613 9799</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>10641409</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="inlineStr"/>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Amber-Distribution-Estonia-616752232134626/</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amberdistributionestonia</t>
+        </is>
+      </c>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>Vahur Kellamov</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vahur-kellamov-a8724087/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>As Avallone</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>As Avallone</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>25006</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>6 Remmelga</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>11215</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://avallone.ee</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>info@avallone.ee</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>+372 682 8800</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>10238895</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr"/>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/avalloneas/</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/avalloneas/</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr">
+        <is>
+          <t>Riho Eensoo</t>
+        </is>
+      </c>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/riho-eensoo-b2a13996</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>As Avallone</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>As Avallone</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>25006</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>6 Remmelga</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>11215</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://avallone.ee</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>info@avallone.ee</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>+372 682 8800</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>10238895</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr"/>
+      <c r="S195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/avalloneas/</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/avalloneas/</t>
+        </is>
+      </c>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr">
+        <is>
+          <t>Rain Kasela</t>
+        </is>
+      </c>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA195" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA195"/>
+  <dimension ref="A1:AA199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21765,6 +21765,434 @@
       </c>
       <c r="AA195" s="2" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Vinodeli Oü</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Vinodeli Oü</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>122290</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>109 Ehitajate tee</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>13514</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://vinodeli.ee</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>info@vinodeli.ee</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr"/>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>16187414</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr"/>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinoDeliTallinn</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinodelitallinn/</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr"/>
+      <c r="X196" s="2" t="inlineStr"/>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Maxima Eesti Oü</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Maxima Eesti Oü</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>22101</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>13 Aiandi</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>12915</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.maxima.ee</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>klienditugi@maxima.ee</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>+372 8002 121</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>10765896</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maxima-eesti-o-/</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maximaeesti/</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maxima.eesti</t>
+        </is>
+      </c>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MaximaEstonia</t>
+        </is>
+      </c>
+      <c r="W197" s="2" t="inlineStr">
+        <is>
+          <t>Diana Gegelyte</t>
+        </is>
+      </c>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diana-gegelyte-0238b6135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Maxima Eesti Oü</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Maxima Eesti Oü</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>22101</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>13 Aiandi</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>12915</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.maxima.ee</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>klienditugi@maxima.ee</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>+372 8002 121</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>10765896</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maxima-eesti-o-/</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maximaeesti/</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maxima.eesti</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MaximaEstonia</t>
+        </is>
+      </c>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>Karina Sabelski</t>
+        </is>
+      </c>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>Director of Purchasing</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/karina-sabelski-9378444/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Maxima Eesti Oü</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Maxima Eesti Oü</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>22101</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>13 Aiandi</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>12915</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.maxima.ee</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>klienditugi@maxima.ee</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>+372 8002 121</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>10765896</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/maxima-eesti-o-/</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maximaeesti/</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maxima.eesti</t>
+        </is>
+      </c>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MaximaEstonia</t>
+        </is>
+      </c>
+      <c r="W199" s="2" t="inlineStr">
+        <is>
+          <t>Nana Kakaladze</t>
+        </is>
+      </c>
+      <c r="X199" s="2" t="inlineStr">
+        <is>
+          <t>Junior Purchasing Specialist</t>
+        </is>
+      </c>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/nana-kakaladze-48b314151/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA199"/>
+  <dimension ref="A1:AA200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22193,6 +22193,87 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Enoteca Nordica Oü</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Enoteca Nordica Oü</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>122284</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>29 Tartu maantee</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>10128</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enoteca.ee</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>info@enoteca.ee</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr"/>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>12325635</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr"/>
+      <c r="S200" s="2" t="inlineStr"/>
+      <c r="T200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr"/>
+      <c r="W200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr"/>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA200"/>
+  <dimension ref="A1:AA201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22274,6 +22274,87 @@
       <c r="Z200" s="2" t="inlineStr"/>
       <c r="AA200" s="2" t="inlineStr"/>
     </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Enoteca Nordica Oü</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Enoteca Nordica Oü</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>122284</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>29 Tartu maantee</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>10128</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enoteca.ee</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>info@enoteca.ee</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr"/>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>12325635</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr"/>
+      <c r="S201" s="2" t="inlineStr"/>
+      <c r="T201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr"/>
+      <c r="W201" s="2" t="inlineStr"/>
+      <c r="X201" s="2" t="inlineStr"/>
+      <c r="Y201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA201"/>
+  <dimension ref="A1:AA202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22355,6 +22355,87 @@
       <c r="Z201" s="2" t="inlineStr"/>
       <c r="AA201" s="2" t="inlineStr"/>
     </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Enoteca Nordica Oü</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Enoteca Nordica Oü</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>122284</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>29 Tartu maantee</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>10128</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enoteca.ee</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>info@enoteca.ee</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr"/>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>12325635</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr"/>
+      <c r="S202" s="2" t="inlineStr"/>
+      <c r="T202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr"/>
+      <c r="W202" s="2" t="inlineStr"/>
+      <c r="X202" s="2" t="inlineStr"/>
+      <c r="Y202" s="2" t="inlineStr"/>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Estonia.xlsx
+++ b/BWI/bestwine_output/bestwine_Estonia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA202"/>
+  <dimension ref="A1:AA203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22436,6 +22436,87 @@
       <c r="Z202" s="2" t="inlineStr"/>
       <c r="AA202" s="2" t="inlineStr"/>
     </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Enoteca Nordica Oü</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Enoteca Nordica Oü</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>122284</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Harju maakond</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>29 Tartu maantee</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>10128</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.enoteca.ee</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>info@enoteca.ee</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr"/>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>12325635</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr"/>
+      <c r="S203" s="2" t="inlineStr"/>
+      <c r="T203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr"/>
+      <c r="X203" s="2" t="inlineStr"/>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
